--- a/data/england/p6_deployment/missing/data_understanding/df_match_player_miss.xlsx
+++ b/data/england/p6_deployment/missing/data_understanding/df_match_player_miss.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,9 +425,2280 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:EY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_3</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_3</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_4</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_4</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_5</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_5</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_6</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_6</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_7</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_7</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_8</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_8</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_9</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_9</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_10</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_10</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_11</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_11</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_1</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_1</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_2</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_2</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_3</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_3</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_4</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_4</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_5</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_5</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_6</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_6</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_7</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_7</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_8</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_8</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_9</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_9</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_10</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_10</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_11</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_11</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_1</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_1</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_2</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_2</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_3</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_3</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_4</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_4</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_5</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_5</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_6</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_6</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_7</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_7</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_8</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_8</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_9</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_9</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_1</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_1</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_2</t>
+        </is>
+      </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_2</t>
+        </is>
+      </c>
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_3</t>
+        </is>
+      </c>
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_3</t>
+        </is>
+      </c>
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_4</t>
+        </is>
+      </c>
+      <c r="BS1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_4</t>
+        </is>
+      </c>
+      <c r="BT1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_5</t>
+        </is>
+      </c>
+      <c r="BU1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_5</t>
+        </is>
+      </c>
+      <c r="BV1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_6</t>
+        </is>
+      </c>
+      <c r="BW1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_6</t>
+        </is>
+      </c>
+      <c r="BX1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_7</t>
+        </is>
+      </c>
+      <c r="BY1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_7</t>
+        </is>
+      </c>
+      <c r="BZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_8</t>
+        </is>
+      </c>
+      <c r="CA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_8</t>
+        </is>
+      </c>
+      <c r="CB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_9</t>
+        </is>
+      </c>
+      <c r="CC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_9</t>
+        </is>
+      </c>
+      <c r="CD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_1</t>
+        </is>
+      </c>
+      <c r="CE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_1</t>
+        </is>
+      </c>
+      <c r="CF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_2</t>
+        </is>
+      </c>
+      <c r="CG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_2</t>
+        </is>
+      </c>
+      <c r="CH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_3</t>
+        </is>
+      </c>
+      <c r="CI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_3</t>
+        </is>
+      </c>
+      <c r="CJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_4</t>
+        </is>
+      </c>
+      <c r="CK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_4</t>
+        </is>
+      </c>
+      <c r="CL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_5</t>
+        </is>
+      </c>
+      <c r="CM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_5</t>
+        </is>
+      </c>
+      <c r="CN1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_6</t>
+        </is>
+      </c>
+      <c r="CO1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_6</t>
+        </is>
+      </c>
+      <c r="CP1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_7</t>
+        </is>
+      </c>
+      <c r="CQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_7</t>
+        </is>
+      </c>
+      <c r="CR1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_8</t>
+        </is>
+      </c>
+      <c r="CS1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_8</t>
+        </is>
+      </c>
+      <c r="CT1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_9</t>
+        </is>
+      </c>
+      <c r="CU1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_9</t>
+        </is>
+      </c>
+      <c r="CV1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_10</t>
+        </is>
+      </c>
+      <c r="CW1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_10</t>
+        </is>
+      </c>
+      <c r="CX1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_11</t>
+        </is>
+      </c>
+      <c r="CY1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_11</t>
+        </is>
+      </c>
+      <c r="CZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_12</t>
+        </is>
+      </c>
+      <c r="DA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_12</t>
+        </is>
+      </c>
+      <c r="DB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_13</t>
+        </is>
+      </c>
+      <c r="DC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_13</t>
+        </is>
+      </c>
+      <c r="DD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_14</t>
+        </is>
+      </c>
+      <c r="DE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_14</t>
+        </is>
+      </c>
+      <c r="DF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_15</t>
+        </is>
+      </c>
+      <c r="DG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_15</t>
+        </is>
+      </c>
+      <c r="DH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_1</t>
+        </is>
+      </c>
+      <c r="DI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_1</t>
+        </is>
+      </c>
+      <c r="DJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_2</t>
+        </is>
+      </c>
+      <c r="DK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_2</t>
+        </is>
+      </c>
+      <c r="DL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_3</t>
+        </is>
+      </c>
+      <c r="DM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_3</t>
+        </is>
+      </c>
+      <c r="DN1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_4</t>
+        </is>
+      </c>
+      <c r="DO1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_4</t>
+        </is>
+      </c>
+      <c r="DP1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_5</t>
+        </is>
+      </c>
+      <c r="DQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_5</t>
+        </is>
+      </c>
+      <c r="DR1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_6</t>
+        </is>
+      </c>
+      <c r="DS1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_6</t>
+        </is>
+      </c>
+      <c r="DT1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_7</t>
+        </is>
+      </c>
+      <c r="DU1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_7</t>
+        </is>
+      </c>
+      <c r="DV1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_8</t>
+        </is>
+      </c>
+      <c r="DW1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_8</t>
+        </is>
+      </c>
+      <c r="DX1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_9</t>
+        </is>
+      </c>
+      <c r="DY1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_9</t>
+        </is>
+      </c>
+      <c r="DZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_10</t>
+        </is>
+      </c>
+      <c r="EA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_10</t>
+        </is>
+      </c>
+      <c r="EB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_11</t>
+        </is>
+      </c>
+      <c r="EC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_11</t>
+        </is>
+      </c>
+      <c r="ED1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_12</t>
+        </is>
+      </c>
+      <c r="EE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_12</t>
+        </is>
+      </c>
+      <c r="EF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_13</t>
+        </is>
+      </c>
+      <c r="EG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_13</t>
+        </is>
+      </c>
+      <c r="EH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_14</t>
+        </is>
+      </c>
+      <c r="EI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_14</t>
+        </is>
+      </c>
+      <c r="EJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_15</t>
+        </is>
+      </c>
+      <c r="EK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_15</t>
+        </is>
+      </c>
+      <c r="EL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_1</t>
+        </is>
+      </c>
+      <c r="EM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_1</t>
+        </is>
+      </c>
+      <c r="EN1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_2</t>
+        </is>
+      </c>
+      <c r="EO1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_2</t>
+        </is>
+      </c>
+      <c r="EP1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_1</t>
+        </is>
+      </c>
+      <c r="EQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_1</t>
+        </is>
+      </c>
+      <c r="ER1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_2</t>
+        </is>
+      </c>
+      <c r="ES1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_2</t>
+        </is>
+      </c>
+      <c r="ET1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_3</t>
+        </is>
+      </c>
+      <c r="EU1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_3</t>
+        </is>
+      </c>
+      <c r="EV1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_4</t>
+        </is>
+      </c>
+      <c r="EW1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_4</t>
+        </is>
+      </c>
+      <c r="EX1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_5</t>
+        </is>
+      </c>
+      <c r="EY1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_5</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>ratYowuH</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>jwRV63z0</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>leno bernd</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>ILahlAf4</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>tete kenny</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>AmMLTTJU</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>andersen joachim</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>faJVc0Mk</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>bassey calvin</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>ppHdaUtm</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>robinson antonee</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>tShG7cpg</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>pereira andreas</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>KCY13JFl</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>berge sander</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>QLwOwRlJ</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>nelson reiss</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>fsJB9j4d</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>smith rowe emile</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>2L5gbR8M</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>iwobi alex</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>ENwqg0Pd</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>jimenez raul</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>INE64p13</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>flekken mark</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>pp1zpsrr</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>roerslev rasmussen mads</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>4AmU39Qm</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>collins nathan</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>EsUW9DS3</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>pinnock ethan</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>6X0pS3GR</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>van den berg sepp</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>E3lsxLi7</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>norgaard christian</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>pSeiTOw5</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>janelt vitaly</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>8KDrOl80</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>mbeumo bryan</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>WIxH5hxa</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>damsgaard mikkel</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>UyeRftbc</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>lewis potter keane</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>b35gWzB2</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>wissa yoane</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>Y9iAmorJ</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>benda steven</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>Uqxm6DaI</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>cairney tom</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>xYfOMcA5</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>castagne timothy</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>Eyqbicqr</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>diop issa</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>rFwPSFb6</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>reed harrison</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>A5ZlWABs</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>rodrigo muniz</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>WOecsPmi</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>sessegnon ryan</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>Qsy3Kmgj</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>traore adama</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>KWbu7UwK</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>wilson harry</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>MqsQc0hn</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>carvalho fabio</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>Aijf2AQ6</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>jensen mathias</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>fysv2qF1</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>konak tan harika yunus emre</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>8fdCpsEA</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
+          <t>maghoma paris</t>
+        </is>
+      </c>
+      <c r="BT2" t="inlineStr">
+        <is>
+          <t>SzUQvQ7r</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
+          <t>mee ben</t>
+        </is>
+      </c>
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>bVI8H8S4</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
+          <t>meghoma jayden</t>
+        </is>
+      </c>
+      <c r="BX2" t="inlineStr">
+        <is>
+          <t>GOPUXXvG</t>
+        </is>
+      </c>
+      <c r="BY2" t="inlineStr">
+        <is>
+          <t>schade kevin</t>
+        </is>
+      </c>
+      <c r="BZ2" t="inlineStr">
+        <is>
+          <t>pCDi9RWI</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
+          <t>valdimarsson hakon</t>
+        </is>
+      </c>
+      <c r="CB2" t="inlineStr">
+        <is>
+          <t>8noY4nKo</t>
+        </is>
+      </c>
+      <c r="CC2" t="inlineStr">
+        <is>
+          <t>yarmolyuk yegor</t>
+        </is>
+      </c>
+      <c r="CD2" t="inlineStr">
+        <is>
+          <t>Qsy3Kmgj</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>traore adama</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
+          <t>Qsy3Kmgj</t>
+        </is>
+      </c>
+      <c r="CG2" t="inlineStr">
+        <is>
+          <t>traore adama</t>
+        </is>
+      </c>
+      <c r="CH2" t="inlineStr">
+        <is>
+          <t>tShG7cpg</t>
+        </is>
+      </c>
+      <c r="CI2" t="inlineStr">
+        <is>
+          <t>pereira andreas</t>
+        </is>
+      </c>
+      <c r="CJ2" t="inlineStr">
+        <is>
+          <t>xYfOMcA5</t>
+        </is>
+      </c>
+      <c r="CK2" t="inlineStr">
+        <is>
+          <t>castagne timothy</t>
+        </is>
+      </c>
+      <c r="CL2" t="inlineStr">
+        <is>
+          <t>xYfOMcA5</t>
+        </is>
+      </c>
+      <c r="CM2" t="inlineStr">
+        <is>
+          <t>castagne timothy</t>
+        </is>
+      </c>
+      <c r="CN2" t="inlineStr">
+        <is>
+          <t>ILahlAf4</t>
+        </is>
+      </c>
+      <c r="CO2" t="inlineStr">
+        <is>
+          <t>tete kenny</t>
+        </is>
+      </c>
+      <c r="CP2" t="inlineStr">
+        <is>
+          <t>A5ZlWABs</t>
+        </is>
+      </c>
+      <c r="CQ2" t="inlineStr">
+        <is>
+          <t>rodrigo muniz</t>
+        </is>
+      </c>
+      <c r="CR2" t="inlineStr">
+        <is>
+          <t>A5ZlWABs</t>
+        </is>
+      </c>
+      <c r="CS2" t="inlineStr">
+        <is>
+          <t>rodrigo muniz</t>
+        </is>
+      </c>
+      <c r="CT2" t="inlineStr">
+        <is>
+          <t>ENwqg0Pd</t>
+        </is>
+      </c>
+      <c r="CU2" t="inlineStr">
+        <is>
+          <t>jimenez raul</t>
+        </is>
+      </c>
+      <c r="CV2" t="inlineStr">
+        <is>
+          <t>KWbu7UwK</t>
+        </is>
+      </c>
+      <c r="CW2" t="inlineStr">
+        <is>
+          <t>wilson harry</t>
+        </is>
+      </c>
+      <c r="CX2" t="inlineStr">
+        <is>
+          <t>KWbu7UwK</t>
+        </is>
+      </c>
+      <c r="CY2" t="inlineStr">
+        <is>
+          <t>wilson harry</t>
+        </is>
+      </c>
+      <c r="CZ2" t="inlineStr">
+        <is>
+          <t>QLwOwRlJ</t>
+        </is>
+      </c>
+      <c r="DA2" t="inlineStr">
+        <is>
+          <t>nelson reiss</t>
+        </is>
+      </c>
+      <c r="DB2" t="inlineStr">
+        <is>
+          <t>Uqxm6DaI</t>
+        </is>
+      </c>
+      <c r="DC2" t="inlineStr">
+        <is>
+          <t>cairney tom</t>
+        </is>
+      </c>
+      <c r="DD2" t="inlineStr">
+        <is>
+          <t>Uqxm6DaI</t>
+        </is>
+      </c>
+      <c r="DE2" t="inlineStr">
+        <is>
+          <t>cairney tom</t>
+        </is>
+      </c>
+      <c r="DF2" t="inlineStr">
+        <is>
+          <t>fsJB9j4d</t>
+        </is>
+      </c>
+      <c r="DG2" t="inlineStr">
+        <is>
+          <t>smith rowe emile</t>
+        </is>
+      </c>
+      <c r="DH2" t="inlineStr">
+        <is>
+          <t>Aijf2AQ6</t>
+        </is>
+      </c>
+      <c r="DI2" t="inlineStr">
+        <is>
+          <t>jensen mathias</t>
+        </is>
+      </c>
+      <c r="DJ2" t="inlineStr">
+        <is>
+          <t>Aijf2AQ6</t>
+        </is>
+      </c>
+      <c r="DK2" t="inlineStr">
+        <is>
+          <t>jensen mathias</t>
+        </is>
+      </c>
+      <c r="DL2" t="inlineStr">
+        <is>
+          <t>WIxH5hxa</t>
+        </is>
+      </c>
+      <c r="DM2" t="inlineStr">
+        <is>
+          <t>damsgaard mikkel</t>
+        </is>
+      </c>
+      <c r="DN2" t="inlineStr">
+        <is>
+          <t>GOPUXXvG</t>
+        </is>
+      </c>
+      <c r="DO2" t="inlineStr">
+        <is>
+          <t>schade kevin</t>
+        </is>
+      </c>
+      <c r="DP2" t="inlineStr">
+        <is>
+          <t>GOPUXXvG</t>
+        </is>
+      </c>
+      <c r="DQ2" t="inlineStr">
+        <is>
+          <t>schade kevin</t>
+        </is>
+      </c>
+      <c r="DR2" t="inlineStr">
+        <is>
+          <t>b35gWzB2</t>
+        </is>
+      </c>
+      <c r="DS2" t="inlineStr">
+        <is>
+          <t>wissa yoane</t>
+        </is>
+      </c>
+      <c r="DT2" t="inlineStr">
+        <is>
+          <t>MqsQc0hn</t>
+        </is>
+      </c>
+      <c r="DU2" t="inlineStr">
+        <is>
+          <t>carvalho fabio</t>
+        </is>
+      </c>
+      <c r="DV2" t="inlineStr">
+        <is>
+          <t>MqsQc0hn</t>
+        </is>
+      </c>
+      <c r="DW2" t="inlineStr">
+        <is>
+          <t>carvalho fabio</t>
+        </is>
+      </c>
+      <c r="DX2" t="inlineStr">
+        <is>
+          <t>UyeRftbc</t>
+        </is>
+      </c>
+      <c r="DY2" t="inlineStr">
+        <is>
+          <t>lewis potter keane</t>
+        </is>
+      </c>
+      <c r="DZ2" t="inlineStr">
+        <is>
+          <t>SzUQvQ7r</t>
+        </is>
+      </c>
+      <c r="EA2" t="inlineStr">
+        <is>
+          <t>mee ben</t>
+        </is>
+      </c>
+      <c r="EB2" t="inlineStr">
+        <is>
+          <t>SzUQvQ7r</t>
+        </is>
+      </c>
+      <c r="EC2" t="inlineStr">
+        <is>
+          <t>mee ben</t>
+        </is>
+      </c>
+      <c r="ED2" t="inlineStr">
+        <is>
+          <t>8KDrOl80</t>
+        </is>
+      </c>
+      <c r="EE2" t="inlineStr">
+        <is>
+          <t>mbeumo bryan</t>
+        </is>
+      </c>
+      <c r="EF2" t="inlineStr">
+        <is>
+          <t>8noY4nKo</t>
+        </is>
+      </c>
+      <c r="EG2" t="inlineStr">
+        <is>
+          <t>yarmolyuk yegor</t>
+        </is>
+      </c>
+      <c r="EH2" t="inlineStr">
+        <is>
+          <t>8noY4nKo</t>
+        </is>
+      </c>
+      <c r="EI2" t="inlineStr">
+        <is>
+          <t>yarmolyuk yegor</t>
+        </is>
+      </c>
+      <c r="EJ2" t="inlineStr">
+        <is>
+          <t>pSeiTOw5</t>
+        </is>
+      </c>
+      <c r="EK2" t="inlineStr">
+        <is>
+          <t>janelt vitaly</t>
+        </is>
+      </c>
+      <c r="EL2" t="inlineStr">
+        <is>
+          <t>jwnLrX9d</t>
+        </is>
+      </c>
+      <c r="EM2" t="inlineStr">
+        <is>
+          <t>carlos vinicius</t>
+        </is>
+      </c>
+      <c r="EN2" t="inlineStr">
+        <is>
+          <t>nwu2UvUA</t>
+        </is>
+      </c>
+      <c r="EO2" t="inlineStr">
+        <is>
+          <t>lukic sasa</t>
+        </is>
+      </c>
+      <c r="EP2" t="inlineStr">
+        <is>
+          <t>6qin1IFT</t>
+        </is>
+      </c>
+      <c r="EQ2" t="inlineStr">
+        <is>
+          <t>da silva joshua</t>
+        </is>
+      </c>
+      <c r="ER2" t="inlineStr">
+        <is>
+          <t>r3Sue7SA</t>
+        </is>
+      </c>
+      <c r="ES2" t="inlineStr">
+        <is>
+          <t>gustavo nunes</t>
+        </is>
+      </c>
+      <c r="ET2" t="inlineStr">
+        <is>
+          <t>tdO4c5vq</t>
+        </is>
+      </c>
+      <c r="EU2" t="inlineStr">
+        <is>
+          <t>henry rico</t>
+        </is>
+      </c>
+      <c r="EV2" t="inlineStr">
+        <is>
+          <t>rcIXJMf9</t>
+        </is>
+      </c>
+      <c r="EW2" t="inlineStr">
+        <is>
+          <t>hickey aaron</t>
+        </is>
+      </c>
+      <c r="EX2" t="inlineStr">
+        <is>
+          <t>MmJb4MzQ</t>
+        </is>
+      </c>
+      <c r="EY2" t="inlineStr">
+        <is>
+          <t>rodriguez thiago</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>vwSGH1jf</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>O4tKqkWE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>goode ben</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>YHcBFRgn</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>stevens connor</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Q7nWkEAh</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>adebiyi callum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>IBmfpp2s</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>gallimore tsharne</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>zw4Qm1Nj</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>lafleur alex</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>82CYpLMk</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lodge ashley</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>fckLsKRT</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>lewis rolfe</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>nuM6lEk7</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>cawley jack</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>fi9FSKGI</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>esan samson</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>W8mlMYBg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>minhas nathan</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>pEnooupQ</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>weiss mitchell</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>QFl5Yq50</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>wickens george</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>QwwXld38</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>o connor paudie</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>UyqjEwmt</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>darikwa tendayi</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>MZYn1eNb</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>roughan sean</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>jPQnWl4p</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>mcgrandles conor</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>AHlngErK</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>ring erik</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>vcxEJQPg</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>mckiernan john joshua</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>E5lapm0O</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>moylan jack</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>zmZsGA5M</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>hackett fairchild reeco</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>ARWEKZLA</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>draper freddie</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>4bpPAQQH</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>makama jovon</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>hWZnRp22</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>brown steve</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>2JjVJSq1</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>clayton bradley</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>jRFgghsg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>connors jack</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>G0blTRIM</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>grant joe</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>YmXMzpl6</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>jones avan</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>bLf0xuu4</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>roberts connor</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>W6dMZudp</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>rowe omar</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>CxyBYiet</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>steinke oliver</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>IgmfNp6D</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>upward ryan</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>fcpYbkRB</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>cadamarteri bailey</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>YcQZnupH</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t>earley saxon</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>4tvwb61E</t>
+        </is>
+      </c>
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>hamilton ethan</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>C4Esu4uR</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
+          <t>house ben</t>
+        </is>
+      </c>
+      <c r="BT3" t="inlineStr">
+        <is>
+          <t>v5aVte64</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
+          <t>jefferies dom</t>
+        </is>
+      </c>
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>b9whdSLf</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
+          <t>okoro zane</t>
+        </is>
+      </c>
+      <c r="BX3" t="inlineStr">
+        <is>
+          <t>EHsnekbs</t>
+        </is>
+      </c>
+      <c r="BY3" t="inlineStr">
+        <is>
+          <t>oliver denny</t>
+        </is>
+      </c>
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>bDjER9xd</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
+          <t>pardington james</t>
+        </is>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>hClSQRsa</t>
+        </is>
+      </c>
+      <c r="CC3" t="inlineStr">
+        <is>
+          <t>parks charlie</t>
+        </is>
+      </c>
+      <c r="CD3" t="inlineStr">
+        <is>
+          <t>YmXMzpl6</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>jones avan</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
+          <t>YmXMzpl6</t>
+        </is>
+      </c>
+      <c r="CG3" t="inlineStr">
+        <is>
+          <t>jones avan</t>
+        </is>
+      </c>
+      <c r="CH3" t="inlineStr">
+        <is>
+          <t>fckLsKRT</t>
+        </is>
+      </c>
+      <c r="CI3" t="inlineStr">
+        <is>
+          <t>lewis rolfe</t>
+        </is>
+      </c>
+      <c r="CJ3" t="inlineStr">
+        <is>
+          <t>W6dMZudp</t>
+        </is>
+      </c>
+      <c r="CK3" t="inlineStr">
+        <is>
+          <t>rowe omar</t>
+        </is>
+      </c>
+      <c r="CL3" t="inlineStr">
+        <is>
+          <t>W6dMZudp</t>
+        </is>
+      </c>
+      <c r="CM3" t="inlineStr">
+        <is>
+          <t>rowe omar</t>
+        </is>
+      </c>
+      <c r="CN3" t="inlineStr">
+        <is>
+          <t>fi9FSKGI</t>
+        </is>
+      </c>
+      <c r="CO3" t="inlineStr">
+        <is>
+          <t>esan samson</t>
+        </is>
+      </c>
+      <c r="CP3" t="inlineStr">
+        <is>
+          <t>IgmfNp6D</t>
+        </is>
+      </c>
+      <c r="CQ3" t="inlineStr">
+        <is>
+          <t>upward ryan</t>
+        </is>
+      </c>
+      <c r="CR3" t="inlineStr">
+        <is>
+          <t>IgmfNp6D</t>
+        </is>
+      </c>
+      <c r="CS3" t="inlineStr">
+        <is>
+          <t>upward ryan</t>
+        </is>
+      </c>
+      <c r="CT3" t="inlineStr">
+        <is>
+          <t>IBmfpp2s</t>
+        </is>
+      </c>
+      <c r="CU3" t="inlineStr">
+        <is>
+          <t>gallimore tsharne</t>
+        </is>
+      </c>
+      <c r="CV3" t="inlineStr">
+        <is>
+          <t>hWZnRp22</t>
+        </is>
+      </c>
+      <c r="CW3" t="inlineStr">
+        <is>
+          <t>brown steve</t>
+        </is>
+      </c>
+      <c r="CX3" t="inlineStr">
+        <is>
+          <t>hWZnRp22</t>
+        </is>
+      </c>
+      <c r="CY3" t="inlineStr">
+        <is>
+          <t>brown steve</t>
+        </is>
+      </c>
+      <c r="CZ3" t="inlineStr">
+        <is>
+          <t>YHcBFRgn</t>
+        </is>
+      </c>
+      <c r="DA3" t="inlineStr">
+        <is>
+          <t>stevens connor</t>
+        </is>
+      </c>
+      <c r="DB3" t="inlineStr">
+        <is>
+          <t>G0blTRIM</t>
+        </is>
+      </c>
+      <c r="DC3" t="inlineStr">
+        <is>
+          <t>grant joe</t>
+        </is>
+      </c>
+      <c r="DD3" t="inlineStr">
+        <is>
+          <t>G0blTRIM</t>
+        </is>
+      </c>
+      <c r="DE3" t="inlineStr">
+        <is>
+          <t>grant joe</t>
+        </is>
+      </c>
+      <c r="DF3" t="inlineStr">
+        <is>
+          <t>W8mlMYBg</t>
+        </is>
+      </c>
+      <c r="DG3" t="inlineStr">
+        <is>
+          <t>minhas nathan</t>
+        </is>
+      </c>
+      <c r="DH3" t="inlineStr">
+        <is>
+          <t>4tvwb61E</t>
+        </is>
+      </c>
+      <c r="DI3" t="inlineStr">
+        <is>
+          <t>hamilton ethan</t>
+        </is>
+      </c>
+      <c r="DJ3" t="inlineStr">
+        <is>
+          <t>4tvwb61E</t>
+        </is>
+      </c>
+      <c r="DK3" t="inlineStr">
+        <is>
+          <t>hamilton ethan</t>
+        </is>
+      </c>
+      <c r="DL3" t="inlineStr">
+        <is>
+          <t>jPQnWl4p</t>
+        </is>
+      </c>
+      <c r="DM3" t="inlineStr">
+        <is>
+          <t>mcgrandles conor</t>
+        </is>
+      </c>
+      <c r="DN3" t="inlineStr">
+        <is>
+          <t>fcpYbkRB</t>
+        </is>
+      </c>
+      <c r="DO3" t="inlineStr">
+        <is>
+          <t>cadamarteri bailey</t>
+        </is>
+      </c>
+      <c r="DP3" t="inlineStr">
+        <is>
+          <t>fcpYbkRB</t>
+        </is>
+      </c>
+      <c r="DQ3" t="inlineStr">
+        <is>
+          <t>cadamarteri bailey</t>
+        </is>
+      </c>
+      <c r="DR3" t="inlineStr">
+        <is>
+          <t>4bpPAQQH</t>
+        </is>
+      </c>
+      <c r="DS3" t="inlineStr">
+        <is>
+          <t>makama jovon</t>
+        </is>
+      </c>
+      <c r="DT3" t="inlineStr">
+        <is>
+          <t>v5aVte64</t>
+        </is>
+      </c>
+      <c r="DU3" t="inlineStr">
+        <is>
+          <t>jefferies dom</t>
+        </is>
+      </c>
+      <c r="DV3" t="inlineStr">
+        <is>
+          <t>v5aVte64</t>
+        </is>
+      </c>
+      <c r="DW3" t="inlineStr">
+        <is>
+          <t>jefferies dom</t>
+        </is>
+      </c>
+      <c r="DX3" t="inlineStr">
+        <is>
+          <t>zmZsGA5M</t>
+        </is>
+      </c>
+      <c r="DY3" t="inlineStr">
+        <is>
+          <t>hackett fairchild reeco</t>
+        </is>
+      </c>
+      <c r="DZ3" t="inlineStr">
+        <is>
+          <t>b9whdSLf</t>
+        </is>
+      </c>
+      <c r="EA3" t="inlineStr">
+        <is>
+          <t>okoro zane</t>
+        </is>
+      </c>
+      <c r="EB3" t="inlineStr">
+        <is>
+          <t>b9whdSLf</t>
+        </is>
+      </c>
+      <c r="EC3" t="inlineStr">
+        <is>
+          <t>okoro zane</t>
+        </is>
+      </c>
+      <c r="ED3" t="inlineStr">
+        <is>
+          <t>ARWEKZLA</t>
+        </is>
+      </c>
+      <c r="EE3" t="inlineStr">
+        <is>
+          <t>draper freddie</t>
+        </is>
+      </c>
+      <c r="EF3" t="inlineStr">
+        <is>
+          <t>YcQZnupH</t>
+        </is>
+      </c>
+      <c r="EG3" t="inlineStr">
+        <is>
+          <t>earley saxon</t>
+        </is>
+      </c>
+      <c r="EH3" t="inlineStr">
+        <is>
+          <t>YcQZnupH</t>
+        </is>
+      </c>
+      <c r="EI3" t="inlineStr">
+        <is>
+          <t>earley saxon</t>
+        </is>
+      </c>
+      <c r="EJ3" t="inlineStr">
+        <is>
+          <t>E5lapm0O</t>
+        </is>
+      </c>
+      <c r="EK3" t="inlineStr">
+        <is>
+          <t>moylan jack</t>
+        </is>
+      </c>
+      <c r="EL3" t="inlineStr"/>
+      <c r="EM3" t="inlineStr"/>
+      <c r="EN3" t="inlineStr"/>
+      <c r="EO3" t="inlineStr"/>
+      <c r="EP3" t="inlineStr"/>
+      <c r="EQ3" t="inlineStr"/>
+      <c r="ER3" t="inlineStr"/>
+      <c r="ES3" t="inlineStr"/>
+      <c r="ET3" t="inlineStr"/>
+      <c r="EU3" t="inlineStr"/>
+      <c r="EV3" t="inlineStr"/>
+      <c r="EW3" t="inlineStr"/>
+      <c r="EX3" t="inlineStr"/>
+      <c r="EY3" t="inlineStr"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>